--- a/pong_dang_project_roadmap.xlsx
+++ b/pong_dang_project_roadmap.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>진행중 (T301/T302 완료, T303 진행 예정)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1103,19 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>46218</v>
+        <v>46214</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>폴더 이동 및 트랙 구조 UI 컴포넌트 구현 — [실제] (일정 조정) T302 완료 다음날로 시작일 당김, 추정 소요일수(4일)는 원안 유지</t>
+          <t>폴더 이동 및 트랙 구조 UI 컴포넌트 구현 — [실제] (일정 조정) T302 완료 다음날로 시작일 당김, 추정 소요일수(4일)는 원안 유지 / [실제] 폴더 CRUD+통계+병합+아이템이동 구현, 실기기에서 생성/이동/통계갱신 검증</t>
         </is>
       </c>
     </row>

--- a/pong_dang_project_roadmap.xlsx
+++ b/pong_dang_project_roadmap.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>진행중 (T401 완료, T402 진행 예정)</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>46232</v>
+        <v>46214</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>46234</v>
+        <v>46214</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>table_calendar 패키지 커스텀 가이드 요청 — [참고] T303 이후(Phase 2/3) 날짜는 원안 그대로 유지된 추정치입니다. T303 진행 상황을 보고 재산정 필요</t>
+          <t>table_calendar 패키지 커스텀 가이드 요청 — [참고] T303 이후(Phase 2/3) 날짜는 원안 그대로 유지된 추정치입니다. T303 진행 상황을 보고 재산정 필요 / [실제] table_calendar 없이 자체 구현. T101처럼 사전 상세 명세서(T401_phase2_feature_spec.md) 작성 후 구현. 실기기 검증 완료</t>
         </is>
       </c>
     </row>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>46235</v>
+        <v>46215</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>46239</v>
+        <v>46219</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>46240</v>
+        <v>46220</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>46242</v>
+        <v>46222</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
